--- a/Assets/Develop/Launcher/GameConfigEC.xlsx
+++ b/Assets/Develop/Launcher/GameConfigEC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\UnityProject\Casuals\Assets\Develop\Launcher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFC7398-E356-4549-9B12-2B9256AE6228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC814CE6-3492-421A-9757-5CDE86854B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4095" yWindow="4815" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubGame" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>GenerateExcelCsharpCode</t>
   </si>
@@ -93,10 +93,6 @@
     <t>Assets/Develop/Lobby/LobbyHomePart/Sprite/icon.png</t>
   </si>
   <si>
-    <t>Skiing.SkiingPlay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -126,13 +122,28 @@
   </si>
   <si>
     <t>Assets/Develop/Lobby/MenuPart/Sprite/gold.png</t>
+  </si>
+  <si>
+    <t>SkiingPlay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScenePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Develop/Skiing/Skiing.unity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +157,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,8 +185,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -450,17 +470,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="18" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,7 +489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -484,8 +505,11 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -501,8 +525,11 @@
       <c r="E3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -518,8 +545,11 @@
       <c r="E4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -533,7 +563,10 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -550,7 +583,7 @@
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -605,16 +638,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -637,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -645,10 +678,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -656,10 +689,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Develop/Launcher/GameConfigEC.xlsx
+++ b/Assets/Develop/Launcher/GameConfigEC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\UnityProject\Casuals\Assets\Develop\Launcher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC814CE6-3492-421A-9757-5CDE86854B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43FD909-D5D2-408A-A44C-BA3552FC9F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SubGame" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>GenerateExcelCsharpCode</t>
   </si>
@@ -90,9 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Develop/Lobby/LobbyHomePart/Sprite/icon.png</t>
-  </si>
-  <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,9 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Develop/Lobby/MenuPart/Sprite/gold.png</t>
-  </si>
-  <si>
     <t>SkiingPlay</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,13 +131,100 @@
   </si>
   <si>
     <t>Assets/Develop/Skiing/Skiing.unity</t>
+  </si>
+  <si>
+    <t>激活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enabled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Develop/DancingLine/DancingLine.unity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会跳舞的线</t>
+  </si>
+  <si>
+    <t>Assets/Develop/JumpJump/JumpJump.unity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Develop/FloorThrottle​/FloorThrottle​.unity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DancingLine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DancingLinePlay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JumpJump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JumpJumpPlay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FloorThrottle​</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FloorThrottle​Play</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoWhiteTile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoWhiteTilePlay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Develop/NoWhiteTile/NoWhiteTile.unity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HexagonMergePlay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HexagonMerge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Develop/HexagonMerge/HexagonMerge.unity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳一跳</t>
+  </si>
+  <si>
+    <t>油门焊死</t>
+  </si>
+  <si>
+    <t>别踩白格</t>
+  </si>
+  <si>
+    <t>六边形合并</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +242,19 @@
     <font>
       <sz val="14"/>
       <color rgb="FF6A9955"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF569CD6"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -185,9 +279,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,18 +570,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="18" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.375" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -497,19 +597,22 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -517,7 +620,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -528,8 +631,11 @@
       <c r="F3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -537,36 +643,139 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>28</v>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -638,16 +847,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -670,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -678,10 +884,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -689,10 +895,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
